--- a/CAP培训_手顺书_学习WBS.xlsx
+++ b/CAP培训_手顺书_学习WBS.xlsx
@@ -766,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4617,6 +4617,390 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>CLI-01</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>把项目切到 Node 22 LTS 并装好依赖（操作型）</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>node -v 输出 v22.x（用 npx -y node@22 -p process.execPath + export PATH 的方式，而不是改系统 Node）；npm install 或 npm ci 成功，npx cds version 能打印 @sap/cds-dk / @sap/cds 版本且没有 ELSPROBLEMS 提示</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>15 分</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>CLI-02</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>用 cds help 自查命令与参数，而不是靠记忆（理解型）</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>能打开 cds help 的总表，并用 cds help &lt;command&gt; 查出至少 5 条本课程用到的命令（init / add / compile / serve / watch / deploy / build / env / bind / lint）；能指出 cd run 与 cd test 不在总帮助列表里但真实存在（cds help run / cds help test 有用法）；能说出 cds install / cds start 这类命令的真实报错形态（Unknown command 'x'. Similar commands are …）</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>15 分</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s3</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>CLI-03</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>用 cds compile 看模型的三份产物（操作型）</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>分别执行 --to sql、--to json（CSN）、--to edmx 各拿到一份产物：SQL 里能看到命名空间前缀的表名与金额列类型、CSN 顶层有 namespace / definitions、EDMX 是 OData V4 且含 EntitySet 与 FunctionImport；再用 --to sql --dialect hana 对比同一实体在 HANA 方言下的列类型差异</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>20 分</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s3-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>CLI-04</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>建库、起服务、看出启动日志的四行关键信息（操作型）</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>npm run deploy 打印 4 行 init from db/data/*.csv 并以 successfully deployed 结束；cds watch（或 npm start）启动日志里能指出：loaded model from N file(s)、connect to db、using auth strategy { kind: 'mocked' }、serving BookOrderService at ['/odata/v4/book-order']；并能说明 cds watch 与 npm start 在「是否监视文件变化」上的差别</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>20 分</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s3-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>CLI-05</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>用 cds env 定位一条「没生效」的配置（排错型）</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>能说出配置来源优先级（内置默认值 → .cdsrc → package.json 的 cds 段 → .cdsrc-private.json → .env → CDS_CONFIG → process.env → VCAP_SERVICES）；用 cds env --sources 列出实际来源，并用 cds env get requires.db 看到 kind: sqlite 与 credentials.url；再用 CDS_requires_db_kind=hana cds env get requires.db.kind 实测出 hana（即环境变量覆盖生效）</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>20 分</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s4</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>CLI-06</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>证明「显式配置会压过 profile 默认值」（排错型）</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>执行 CDS_ENV=production cds env get requires.auth.kind，实测得到 mocked（而不是 production 默认的 jwt），并能解释原因；随后把配置改成按 profile 写（[development] mocked / [production] jwt）并说明上云前为什么必须这么改</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>15 分</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>CLI-07</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>用 curl 拿到 200 / 401 / 404 / 405 / 409 五种状态码（操作型）</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>用 -u alice:alice 与 -o /dev/null -w '%{http_code}' 分别复现：带认证读实体集 → 200；不带认证 → 401；函数查不存在的订单号 → 404；POST 只读的 OrderItemView → 405；重复提交已提交订单（或草稿激活订单号重复）→ 409；并说明每种码对应的业务含义</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>25 分</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s6-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>CLI-08</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>用 curl 调用函数与绑定动作（操作型）</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>GET /getOrderTotal(orderNo='BO-1003') 返回 {"value":17400}；GET /getOrderSummary() 返回 4 行；POST /BookOrders(ID=&lt;uuid&gt;,IsActiveEntity=true)/submitOrder 返回 200 且该订单 status 变成 SUBMITTED；能说明函数为什么用 GET、动作为什么用 POST，以及 IsActiveEntity 的含义</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>25 分</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s6-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>CLI-09</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>看 $metadata 里的注解，判断模型改对了没有（操作型）</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>把 $metadata 存成文件并用 grep 统计 Annotation Term：能看到 Common.Label（来自 @title）、Core.Computed、Common.DraftRoot，以及 draftActivate / draftEdit / draftPrepare 与 IsActiveEntity 存在；能据此判断「注解有没有真的进元数据」而不用等界面</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>20 分</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s7-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>CLI-10</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>把构建到部署的四步命令写进笔记并核对产物名（操作型）</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>写出 cds build --production → mbt build -t mta_archives → cf deploy mta_archives/demo-node_1.0.0.mtar → curl 路由 $metadata 的完整链条，并说明 .mtar 文件名来自 mta.yaml 的 ID/version、云端端口是 8080、判据是 Process finished.（cf 未安装时以官方文档与画面为准，需在相应标注 ~ 的位置注明）</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>15 分</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s8-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>CLI-11</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>用 CAP Java 的 mvn 命令跑起来并说明与 Node 的对照（操作型）</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>在 Java 项目 srv/ 下 mvn spring-boot:run 起服务、mvn -pl srv -am clean install 只构建该模块；能列出 cds-maven-plugin 的 goal（build / watch / auto-build / generate / clean / add / cds / npm / npx 等）并说明 mvn -o 的用途与失效场景；能对照 Node 侧 cds serve / cds watch / npm test 写出等价命令</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>25 分</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s10</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>CLI-12</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>把「目的 → 命令」的决策表整理成自己的速查卡（理解型）</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>从 §11 决策表里自选 10 条，写出「目的 / 命令 / 在哪个目录执行」三列，且没有一条写错目录或漏掉前置（如 cf login、cf target、cds deploy 后要重启服务）；能明确说出三条「不要做」：不要在 srv/ 里敲 cds、不要把 mocked / dummy 认证带上云、不要用 cds watch 做验收或 CI</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>20 分</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4628,7 +5012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8723,9 +9107,417 @@
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>CLI-01</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>把项目切到 Node 22 LTS 并装好依赖（操作型）</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>node -v 输出 v22.x（用 npx -y node@22 -p process.execPath + export PATH 的方式，而不是改系统 Node）；npm install 或 npm ci 成功，npx cds version 能打印 @sap/cds-dk / @sap/cds 版本且没有 ELSPROBLEMS 提示</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>15 分</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s2</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>CLI-02</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>用 cds help 自查命令与参数，而不是靠记忆（理解型）</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>能打开 cds help 的总表，并用 cds help &lt;command&gt; 查出至少 5 条本课程用到的命令（init / add / compile / serve / watch / deploy / build / env / bind / lint）；能指出 cd run 与 cd test 不在总帮助列表里但真实存在（cds help run / cds help test 有用法）；能说出 cds install / cds start 这类命令的真实报错形态（Unknown command 'x'. Similar commands are …）</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>15 分</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s3</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>CLI-03</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>用 cds compile 看模型的三份产物（操作型）</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>分别执行 --to sql、--to json（CSN）、--to edmx 各拿到一份产物：SQL 里能看到命名空间前缀的表名与金额列类型、CSN 顶层有 namespace / definitions、EDMX 是 OData V4 且含 EntitySet 与 FunctionImport；再用 --to sql --dialect hana 对比同一实体在 HANA 方言下的列类型差异</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>20 分</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s3-2</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>CLI-04</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>建库、起服务、看出启动日志的四行关键信息（操作型）</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>npm run deploy 打印 4 行 init from db/data/*.csv 并以 successfully deployed 结束；cds watch（或 npm start）启动日志里能指出：loaded model from N file(s)、connect to db、using auth strategy { kind: 'mocked' }、serving BookOrderService at ['/odata/v4/book-order']；并能说明 cds watch 与 npm start 在「是否监视文件变化」上的差别</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>20 分</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s3-3</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>CLI-05</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>用 cds env 定位一条「没生效」的配置（排错型）</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>能说出配置来源优先级（内置默认值 → .cdsrc → package.json 的 cds 段 → .cdsrc-private.json → .env → CDS_CONFIG → process.env → VCAP_SERVICES）；用 cds env --sources 列出实际来源，并用 cds env get requires.db 看到 kind: sqlite 与 credentials.url；再用 CDS_requires_db_kind=hana cds env get requires.db.kind 实测出 hana（即环境变量覆盖生效）</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>20 分</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s4</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>CLI-06</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>证明「显式配置会压过 profile 默认值」（排错型）</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>执行 CDS_ENV=production cds env get requires.auth.kind，实测得到 mocked（而不是 production 默认的 jwt），并能解释原因；随后把配置改成按 profile 写（[development] mocked / [production] jwt）并说明上云前为什么必须这么改</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>15 分</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s4-3</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>CLI-07</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>用 curl 拿到 200 / 401 / 404 / 405 / 409 五种状态码（操作型）</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>用 -u alice:alice 与 -o /dev/null -w '%{http_code}' 分别复现：带认证读实体集 → 200；不带认证 → 401；函数查不存在的订单号 → 404；POST 只读的 OrderItemView → 405；重复提交已提交订单（或草稿激活订单号重复）→ 409；并说明每种码对应的业务含义</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>25 分</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s6-4</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>CLI-08</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>用 curl 调用函数与绑定动作（操作型）</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>GET /getOrderTotal(orderNo='BO-1003') 返回 {"value":17400}；GET /getOrderSummary() 返回 4 行；POST /BookOrders(ID=&lt;uuid&gt;,IsActiveEntity=true)/submitOrder 返回 200 且该订单 status 变成 SUBMITTED；能说明函数为什么用 GET、动作为什么用 POST，以及 IsActiveEntity 的含义</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>25 分</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s6-2</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>CLI-09</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>看 $metadata 里的注解，判断模型改对了没有（操作型）</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>把 $metadata 存成文件并用 grep 统计 Annotation Term：能看到 Common.Label（来自 @title）、Core.Computed、Common.DraftRoot，以及 draftActivate / draftEdit / draftPrepare 与 IsActiveEntity 存在；能据此判断「注解有没有真的进元数据」而不用等界面</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>20 分</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s7-2</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>CLI-10</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>把构建到部署的四步命令写进笔记并核对产物名（操作型）</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>写出 cds build --production → mbt build -t mta_archives → cf deploy mta_archives/demo-node_1.0.0.mtar → curl 路由 $metadata 的完整链条，并说明 .mtar 文件名来自 mta.yaml 的 ID/version、云端端口是 8080、判据是 Process finished.（cf 未安装时以官方文档与画面为准，需在相应标注 ~ 的位置注明）</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>15 分</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s8-1</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>CLI-11</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>用 CAP Java 的 mvn 命令跑起来并说明与 Node 的对照（操作型）</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>在 Java 项目 srv/ 下 mvn spring-boot:run 起服务、mvn -pl srv -am clean install 只构建该模块；能列出 cds-maven-plugin 的 goal（build / watch / auto-build / generate / clean / add / cds / npm / npx 等）并说明 mvn -o 的用途与失效场景；能对照 Node 侧 cds serve / cds watch / npm test 写出等价命令</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>25 分</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s10</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>命令速查</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>CLI-12</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>把「目的 → 命令」的决策表整理成自己的速查卡（理解型）</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>从 §11 决策表里自选 10 条，写出「目的 / 命令 / 在哪个目录执行」三列，且没有一条写错目录或漏掉前置（如 cf login、cf target、cds deploy 后要重启服务）；能明确说出三条「不要做」：不要在 srv/ 里敲 cds、不要把 mocked / dummy 认证带上云、不要用 cds watch 做验收或 CI</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>20 分</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>cli.html#s11</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"○,△,×"</formula1>
     </dataValidation>
   </dataValidations>
